--- a/Power BI Class Files/Projects/Employess analysis Project/Data File.xlsx
+++ b/Power BI Class Files/Projects/Employess analysis Project/Data File.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\deves\Desktop\Power BI\Learning Projects\Employee data analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\deves\Documents\GitHub\Free_Datasets\Power BI Class Files\Projects\Employess analysis Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC066D55-EC69-40E4-A997-345A95E8D459}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F0A1A04-EFFA-4F64-8D62-227C0C9E7458}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="employees" sheetId="1" r:id="rId1"/>
@@ -1036,7 +1036,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="165" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="164" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -1093,8 +1093,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="2" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1382,9 +1382,9 @@
     <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="21.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="4.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.28515625" customWidth="1"/>
+    <col min="5" max="5" width="11.5703125" customWidth="1"/>
+    <col min="6" max="6" width="12.7109375" style="4" customWidth="1"/>
     <col min="7" max="7" width="13.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
